--- a/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
+++ b/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rc7140c9250164775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rbe5f3bde53d74296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R754e4b4c93434103"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="R85d4b27c7fbe40f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R35418652ef7c42df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R0c9c6509a95f4a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="R0ba9631fea43420a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R1478e7f97e574cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6ae437d0af9b425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rba93d0cecde24437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="Rfc773e39aa854040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Re6f4727aa636489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R619713861bd04f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R8d791ced732a4f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rb862c80ea3604196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R355cfed842854733"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -864,7 +864,7 @@
       <x:c r="D16" s="21"/>
       <x:c r="E16" s="21"/>
       <x:c r="F16" s="22" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="G16" s="22"/>
       <x:c r="H16" s="22"/>
@@ -924,7 +924,7 @@
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
       <x:c r="B23" s="29" t="str">
-        <x:v>適用テンプレート：01C Ver.1.3。React版26画面。基準BL-2026-09-24と個別改訂を参照。02 Ver.2.6・10 Ver.2.7のMenu Code契約を反映。U-01対応済（Closed）（2026-09-29）。文書状態：Review OK（正式承認前）、正式承認は別途記録。</x:v>
+        <x:v>適用テンプレート：01C Ver.1.3。React版26画面。基準BL-2026-09-24と個別改訂を参照。02 Ver.2.6・10 Ver.2.7のMenu Code契約とCFG-05を照合済。U-01 Closed（2026-09-29）。文書状態：Review済／承認待ち。正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="C23" s="29"/>
       <x:c r="D23" s="29"/>
@@ -1301,15 +1301,31 @@
       <x:c r="K12" s="73"/>
       <x:c r="L12" s="73"/>
     </x:row>
-    <x:row r="13" ht="20" customHeight="1">
-      <x:c r="A13" s="73"/>
-      <x:c r="B13" s="73"/>
-      <x:c r="C13" s="73"/>
-      <x:c r="D13" s="73"/>
-      <x:c r="E13" s="73"/>
-      <x:c r="F13" s="73"/>
-      <x:c r="G13" s="73"/>
-      <x:c r="H13" s="73"/>
+    <x:row r="13" ht="100" customHeight="1">
+      <x:c r="A13" s="73" t="str">
+        <x:v>Ver.1.4</x:v>
+      </x:c>
+      <x:c r="B13" s="73" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C13" s="73" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D13" s="73" t="str">
+        <x:v>上流02 Ver.2.6／10 Ver.2.7とMenu契約を再照合。参照をSection／項目単位へ整理。Error Code欄・文書状態を統一。処理Flow・63件UTは変更なし。</x:v>
+      </x:c>
+      <x:c r="E13" s="73" t="str">
+        <x:v>未記入</x:v>
+      </x:c>
+      <x:c r="F13" s="73" t="str">
+        <x:v>未確認</x:v>
+      </x:c>
+      <x:c r="G13" s="73" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="H13" s="73" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
       <x:c r="I13" s="73"/>
       <x:c r="J13" s="73"/>
       <x:c r="K13" s="73"/>
@@ -3470,7 +3486,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -4160,15 +4176,15 @@
       <x:c r="L36" s="73"/>
       <x:c r="M36"/>
     </x:row>
-    <x:row r="37" ht="125" customHeight="1">
+    <x:row r="37" ht="140" customHeight="1">
       <x:c r="A37" s="88" t="str">
         <x:v>U-01／対応済（Closed）</x:v>
       </x:c>
       <x:c r="B37" s="88" t="str">
-        <x:v>2026-09-29：Menu Codeを02で確定し、10のmenus契約へ反映。表示名ではなく固定Codeを受け渡す。</x:v>
+        <x:v>Menu Codeを02 Ver.2.6で正式定義し、10 Ver.2.7のAUTH-004 menus契約へ反映済み。CFG-05との14件の整合確認完了。U-01 Closed。</x:v>
       </x:c>
       <x:c r="C37" s="88" t="str">
-        <x:v>02_権限基本設計書／10_メニュー権限!A25:F41；10／23_API項目定義!A45:K45・A328:K328</x:v>
+        <x:v>02 Ver.2.6／10_メニュー権限 2節「Menu Code定義」・3節「Menu生成・利用規則」。10 Ver.2.7／23_API項目定義 API-AUTH-004 user.menus・menus[]。</x:v>
       </x:c>
       <x:c r="D37" s="88" t="str">
         <x:v>14個のMenu Code・名称・画面・順序・Query・Role／Permission参照とAPI menus契約を照合済。CFG-05・S022・UT-034～036/057～063は維持。未決事項0件。正式承認は別途。</x:v>
@@ -5949,8 +5965,8 @@
     <x:mergeCell ref="C5:H5"/>
     <x:mergeCell ref="I5:J5"/>
     <x:mergeCell ref="K5:L5"/>
+    <x:mergeCell ref="A35:D35"/>
     <x:mergeCell ref="C4:H4"/>
-    <x:mergeCell ref="A35:D35"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6032,7 +6048,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -6345,7 +6361,7 @@
         <x:v>未保存取消／Guard拒否</x:v>
       </x:c>
       <x:c r="I14" s="89" t="str">
-        <x:v>新規Codeなし</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="J14" s="89" t="str">
         <x:v>同期／Dialog待ち</x:v>
@@ -6501,7 +6517,7 @@
         <x:v>Session変更時再Guard</x:v>
       </x:c>
       <x:c r="I18" s="89" t="str">
-        <x:v>新規Codeなし</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="J18" s="89" t="str">
         <x:v>同期</x:v>
@@ -7857,7 +7873,7 @@
         <x:v>S020/S080</x:v>
       </x:c>
       <x:c r="L55" s="88" t="str">
-        <x:v>技術選定書（Company_WorkHub_技术选型.md）</x:v>
+        <x:v>技術選定書</x:v>
       </x:c>
       <x:c r="M55"/>
     </x:row>
@@ -9441,7 +9457,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -9799,7 +9815,7 @@
         <x:v>S022/S030</x:v>
       </x:c>
       <x:c r="K15" s="88" t="str">
-        <x:v>02_権限基本設計書／10_メニュー権限!A25:F53</x:v>
+        <x:v>02 Ver.2.6／10_メニュー権限 2節・3節</x:v>
       </x:c>
       <x:c r="L15" s="88" t="str">
         <x:v>未知値は無視、重複は表示時集約。PathはCFG-01から解決。</x:v>
@@ -13085,7 +13101,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -13551,7 +13567,7 @@
         <x:v>未登録／形式NG:S014</x:v>
       </x:c>
       <x:c r="H18" s="89" t="str">
-        <x:v>新規Codeなし</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="I18" s="89" t="str">
         <x:v>非対象</x:v>
@@ -13989,7 +14005,7 @@
         <x:v>－</x:v>
       </x:c>
       <x:c r="K29" s="88" t="str">
-        <x:v>02_権限基本設計書／10_メニュー権限／10_API共通と認証_基本設計書／23_API項目定義!A45:K45・A328:K328</x:v>
+        <x:v>02 Ver.2.6／10_メニュー権限 2節・3節。10 Ver.2.7／23_API項目定義 API-AUTH-004 user.menus・menus[]</x:v>
       </x:c>
       <x:c r="L29" s="88" t="str">
         <x:v>－</x:v>
@@ -16492,7 +16508,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -16729,7 +16745,7 @@
         <x:v>Navigation</x:v>
       </x:c>
       <x:c r="D13" s="88" t="str">
-        <x:v>－（API Error新設なし）</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="E13" s="88" t="str">
         <x:v>DIRECT:MSG-E-002／redirect拒否:－</x:v>
@@ -19325,8 +19341,8 @@
     <x:mergeCell ref="C5:H5"/>
     <x:mergeCell ref="I5:J5"/>
     <x:mergeCell ref="K5:L5"/>
+    <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="C4:H4"/>
-    <x:mergeCell ref="A7:L7"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -19408,7 +19424,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -23354,8 +23370,8 @@
     <x:mergeCell ref="I5:J5"/>
     <x:mergeCell ref="K5:L5"/>
     <x:mergeCell ref="A82:L82"/>
+    <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="C4:H4"/>
-    <x:mergeCell ref="A7:L7"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
+++ b/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6ae437d0af9b425c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rba93d0cecde24437"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="Rfc773e39aa854040"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Re6f4727aa636489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R619713861bd04f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R8d791ced732a4f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rb862c80ea3604196"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R355cfed842854733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re93fc20bb10f418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R12c00da270c8449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R06846dd5260a41fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Rbbc3c04f246d45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="Rb5025af450a144e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R12a4c9608a5a4cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rdfd4ef8d07844518"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="Rd4e41122058b4e49"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -273,7 +273,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="106">
+  <x:cellXfs count="109">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -510,6 +510,13 @@
     <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -903,7 +910,7 @@
       <x:c r="D19" s="21"/>
       <x:c r="E19" s="21"/>
       <x:c r="F19" s="26" t="str">
-        <x:v>未確認</x:v>
+        <x:v>Review済（署名時記入）</x:v>
       </x:c>
       <x:c r="G19" s="26"/>
       <x:c r="H19" s="26"/>
@@ -916,15 +923,15 @@
       <x:c r="D20" s="21"/>
       <x:c r="E20" s="21"/>
       <x:c r="F20" s="26" t="str">
-        <x:v>未承認</x:v>
+        <x:v>承認待ち（署名時記入）</x:v>
       </x:c>
       <x:c r="G20" s="26"/>
       <x:c r="H20" s="26"/>
       <x:c r="I20" s="26"/>
     </x:row>
-    <x:row r="23" ht="28" customHeight="1">
+    <x:row r="23" ht="100" customHeight="1">
       <x:c r="B23" s="29" t="str">
-        <x:v>適用テンプレート：01C Ver.1.3。React版26画面。基準BL-2026-09-24と個別改訂を参照。02 Ver.2.6・10 Ver.2.7のMenu Code契約とCFG-05を照合済。U-01 Closed（2026-09-29）。文書状態：Review済／承認待ち。正式承認はProject Leaderが記録する。</x:v>
+        <x:v>適用テンプレート：01C Ver.1.3。React版26画面。基準BL-2026-09-24と個別改訂を参照。02 Ver.2.6・10 Ver.2.7のMenu Code契約とCFG-05を照合済。U-01 Closed（2026-09-29）。文書状態：Review済／承認待ち。正式承認はProject Leaderが記録する。 二次Review日：2026-09-30。</x:v>
       </x:c>
       <x:c r="C23" s="29"/>
       <x:c r="D23" s="29"/>
@@ -995,13 +1002,13 @@
     <x:mergeCell ref="C18:E18"/>
     <x:mergeCell ref="F18:I18"/>
     <x:mergeCell ref="C19:E19"/>
-    <x:mergeCell ref="F19:I19"/>
     <x:mergeCell ref="C20:E20"/>
-    <x:mergeCell ref="F20:I20"/>
     <x:mergeCell ref="B10:K12"/>
     <x:mergeCell ref="F15:I15"/>
     <x:mergeCell ref="F16:I16"/>
     <x:mergeCell ref="B23:K27"/>
+    <x:mergeCell ref="F19:I19"/>
+    <x:mergeCell ref="F20:I20"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1083,7 +1090,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -1331,15 +1338,31 @@
       <x:c r="K13" s="73"/>
       <x:c r="L13" s="73"/>
     </x:row>
-    <x:row r="14" ht="20" customHeight="1">
-      <x:c r="A14" s="73"/>
-      <x:c r="B14" s="73"/>
-      <x:c r="C14" s="73"/>
-      <x:c r="D14" s="73"/>
-      <x:c r="E14" s="73"/>
-      <x:c r="F14" s="73"/>
-      <x:c r="G14" s="73"/>
-      <x:c r="H14" s="73"/>
+    <x:row r="14" ht="84" customHeight="1">
+      <x:c r="A14" s="74" t="str">
+        <x:v>Ver.1.4</x:v>
+      </x:c>
+      <x:c r="B14" s="108" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C14" s="74" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="D14" s="74" t="str">
+        <x:v>二次Review完了。Header版数、後続成果物参照、Message Sheet名、文書状態を整理。Flow・UT変更なし。</x:v>
+      </x:c>
+      <x:c r="E14" s="74" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F14" s="74" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="G14" s="74" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H14" s="74" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
       <x:c r="I14" s="73"/>
       <x:c r="J14" s="73"/>
       <x:c r="K14" s="73"/>
@@ -4045,7 +4068,7 @@
         <x:v>CMN-FE-002</x:v>
       </x:c>
       <x:c r="C30" s="89" t="str">
-        <x:v>02_CMN-FE-002_Axios通信・Token更新・共通Error詳細設計書</x:v>
+        <x:v>現在の正本：10_API共通と認証_基本設計書／19_API共通I-O。後続成果物：CMN-FE-002。</x:v>
       </x:c>
       <x:c r="D30" s="89" t="str">
         <x:v>HTTP・Cookie・Refresh1回・Schema検証・追跡IDは委譲。旧版と差がある場合は基本設計10を優先。</x:v>
@@ -4067,8 +4090,8 @@
       <x:c r="B31" s="88" t="str">
         <x:v>CMN-FE-003</x:v>
       </x:c>
-      <x:c r="C31" s="88" t="str">
-        <x:v>03_CMN-FE-003_Form・Validation・Message・Loading詳細設計書</x:v>
+      <x:c r="C31" s="106" t="str">
+        <x:v>現在の正本：03_画面共通設計書／21_ValidationLifecycle、18_メッセージと例外_基本設計書／31_メッセージ。後続成果物：CMN-FE-003。</x:v>
       </x:c>
       <x:c r="D31" s="88" t="str">
         <x:v>Message ID展開、Dialog、Loading部品を利用。最終文言は18のみ。</x:v>
@@ -16730,7 +16753,7 @@
         <x:v>なし</x:v>
       </x:c>
       <x:c r="L12" s="89" t="str">
-        <x:v>18_メッセージと例外_基本設計書／31・31B／31B!A44:F45</x:v>
+        <x:v>18_メッセージと例外_基本設計書／31B_ErrorMessage対応!A44:F45</x:v>
       </x:c>
       <x:c r="M12"/>
     </x:row>

--- a/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
+++ b/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re93fc20bb10f418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R12c00da270c8449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R06846dd5260a41fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Rbbc3c04f246d45e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="Rb5025af450a144e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R12a4c9608a5a4cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rdfd4ef8d07844518"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="Rd4e41122058b4e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6ae437d0af9b425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rba93d0cecde24437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="Rfc773e39aa854040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Re6f4727aa636489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R619713861bd04f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R8d791ced732a4f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rb862c80ea3604196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R355cfed842854733"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -273,7 +273,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="109">
+  <x:cellXfs count="106">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -510,13 +510,6 @@
     <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -910,7 +903,7 @@
       <x:c r="D19" s="21"/>
       <x:c r="E19" s="21"/>
       <x:c r="F19" s="26" t="str">
-        <x:v>Review済（署名時記入）</x:v>
+        <x:v>未確認</x:v>
       </x:c>
       <x:c r="G19" s="26"/>
       <x:c r="H19" s="26"/>
@@ -923,15 +916,15 @@
       <x:c r="D20" s="21"/>
       <x:c r="E20" s="21"/>
       <x:c r="F20" s="26" t="str">
-        <x:v>承認待ち（署名時記入）</x:v>
+        <x:v>未承認</x:v>
       </x:c>
       <x:c r="G20" s="26"/>
       <x:c r="H20" s="26"/>
       <x:c r="I20" s="26"/>
     </x:row>
-    <x:row r="23" ht="100" customHeight="1">
+    <x:row r="23" ht="28" customHeight="1">
       <x:c r="B23" s="29" t="str">
-        <x:v>適用テンプレート：01C Ver.1.3。React版26画面。基準BL-2026-09-24と個別改訂を参照。02 Ver.2.6・10 Ver.2.7のMenu Code契約とCFG-05を照合済。U-01 Closed（2026-09-29）。文書状態：Review済／承認待ち。正式承認はProject Leaderが記録する。 二次Review日：2026-09-30。</x:v>
+        <x:v>適用テンプレート：01C Ver.1.3。React版26画面。基準BL-2026-09-24と個別改訂を参照。02 Ver.2.6・10 Ver.2.7のMenu Code契約とCFG-05を照合済。U-01 Closed（2026-09-29）。文書状態：Review済／承認待ち。正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="C23" s="29"/>
       <x:c r="D23" s="29"/>
@@ -1002,13 +995,13 @@
     <x:mergeCell ref="C18:E18"/>
     <x:mergeCell ref="F18:I18"/>
     <x:mergeCell ref="C19:E19"/>
+    <x:mergeCell ref="F19:I19"/>
     <x:mergeCell ref="C20:E20"/>
+    <x:mergeCell ref="F20:I20"/>
     <x:mergeCell ref="B10:K12"/>
     <x:mergeCell ref="F15:I15"/>
     <x:mergeCell ref="F16:I16"/>
     <x:mergeCell ref="B23:K27"/>
-    <x:mergeCell ref="F19:I19"/>
-    <x:mergeCell ref="F20:I20"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1090,7 +1083,7 @@
       </x:c>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.4</x:v>
+        <x:v>Ver.1.3</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -1338,31 +1331,15 @@
       <x:c r="K13" s="73"/>
       <x:c r="L13" s="73"/>
     </x:row>
-    <x:row r="14" ht="84" customHeight="1">
-      <x:c r="A14" s="74" t="str">
-        <x:v>Ver.1.4</x:v>
-      </x:c>
-      <x:c r="B14" s="108" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="C14" s="74" t="str">
-        <x:v>Review</x:v>
-      </x:c>
-      <x:c r="D14" s="74" t="str">
-        <x:v>二次Review完了。Header版数、後続成果物参照、Message Sheet名、文書状態を整理。Flow・UT変更なし。</x:v>
-      </x:c>
-      <x:c r="E14" s="74" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="F14" s="74" t="str">
-        <x:v>Review済</x:v>
-      </x:c>
-      <x:c r="G14" s="74" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="H14" s="74" t="str">
-        <x:v>承認待ち</x:v>
-      </x:c>
+    <x:row r="14" ht="20" customHeight="1">
+      <x:c r="A14" s="73"/>
+      <x:c r="B14" s="73"/>
+      <x:c r="C14" s="73"/>
+      <x:c r="D14" s="73"/>
+      <x:c r="E14" s="73"/>
+      <x:c r="F14" s="73"/>
+      <x:c r="G14" s="73"/>
+      <x:c r="H14" s="73"/>
       <x:c r="I14" s="73"/>
       <x:c r="J14" s="73"/>
       <x:c r="K14" s="73"/>
@@ -4068,7 +4045,7 @@
         <x:v>CMN-FE-002</x:v>
       </x:c>
       <x:c r="C30" s="89" t="str">
-        <x:v>現在の正本：10_API共通と認証_基本設計書／19_API共通I-O。後続成果物：CMN-FE-002。</x:v>
+        <x:v>02_CMN-FE-002_Axios通信・Token更新・共通Error詳細設計書</x:v>
       </x:c>
       <x:c r="D30" s="89" t="str">
         <x:v>HTTP・Cookie・Refresh1回・Schema検証・追跡IDは委譲。旧版と差がある場合は基本設計10を優先。</x:v>
@@ -4090,8 +4067,8 @@
       <x:c r="B31" s="88" t="str">
         <x:v>CMN-FE-003</x:v>
       </x:c>
-      <x:c r="C31" s="106" t="str">
-        <x:v>現在の正本：03_画面共通設計書／21_ValidationLifecycle、18_メッセージと例外_基本設計書／31_メッセージ。後続成果物：CMN-FE-003。</x:v>
+      <x:c r="C31" s="88" t="str">
+        <x:v>03_CMN-FE-003_Form・Validation・Message・Loading詳細設計書</x:v>
       </x:c>
       <x:c r="D31" s="88" t="str">
         <x:v>Message ID展開、Dialog、Loading部品を利用。最終文言は18のみ。</x:v>
@@ -16753,7 +16730,7 @@
         <x:v>なし</x:v>
       </x:c>
       <x:c r="L12" s="89" t="str">
-        <x:v>18_メッセージと例外_基本設計書／31B_ErrorMessage対応!A44:F45</x:v>
+        <x:v>18_メッセージと例外_基本設計書／31・31B／31B!A44:F45</x:v>
       </x:c>
       <x:c r="M12"/>
     </x:row>

--- a/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
+++ b/詳細設計/共通処理詳細設計/01_CMN-FE-001_Reactアプリ初期化・Route・共通Layout詳細設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re93fc20bb10f418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R12c00da270c8449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R06846dd5260a41fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Rbbc3c04f246d45e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="Rb5025af450a144e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R12a4c9608a5a4cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rdfd4ef8d07844518"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="Rd4e41122058b4e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R24174ea5dfdb419a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R00a61e4455b440bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R6cb6aebbca624888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="R2b895328e872443d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R9218960592fa425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R8f2909d3deab4be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rceb43115deb74ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R2d3562c251cf4060"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3601,10 +3601,10 @@
         <x:v>CMN-FE-001</x:v>
       </x:c>
       <x:c r="C9" s="88" t="str">
-        <x:v>00_詳細設計成果物一覧／03_成果物一覧!C97</x:v>
+        <x:v>本書表紙／ファイル名</x:v>
       </x:c>
       <x:c r="D9" s="88" t="str">
-        <x:v>成果物一覧と同一ID</x:v>
+        <x:v>共通処理IDは表紙、ファイル名および本文内で一致させる。</x:v>
       </x:c>
       <x:c r="E9" s="73"/>
       <x:c r="F9" s="73"/>
